--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R0c1840d0300f4bbb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb2c66bb9e2d47cb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Ra54adb70efc84f9b" tooltip="Open in browser"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R7bccd93441be40a1" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rdb2c66bb9e2d47cb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R020840f740774d47"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R7bccd93441be40a1" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R9913e87efd2c4134" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R020840f740774d47"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45b7c5165ea24020"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R9913e87efd2c4134" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rb1027d41fe664bc0" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R45b7c5165ea24020"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4da0686a0a8f4c3a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rb1027d41fe664bc0" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R59d8b980d5a045c0" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R4da0686a0a8f4c3a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbea19ae82a7342f2"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R59d8b980d5a045c0" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R704843e4830340ed" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbea19ae82a7342f2"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea90b4815d42404d"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R704843e4830340ed" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd2caa6f1e2fb491d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rea90b4815d42404d"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ef0eadaf1994106"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd2caa6f1e2fb491d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Raf2a5ad352054b5d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R9ef0eadaf1994106"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb56ea7259ac64f4f"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Raf2a5ad352054b5d" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R508e090de4334f37" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb56ea7259ac64f4f"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49d40703d99546dc"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R508e090de4334f37" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd19eb8bdc5944e2c" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R49d40703d99546dc"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R197b39ee3b8d4205"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rd19eb8bdc5944e2c" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rb80c6a01a0a5427c" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R197b39ee3b8d4205"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R325fbdf50ab747d0"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rb80c6a01a0a5427c" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rb8a7b2842fcd45a1" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R325fbdf50ab747d0"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra366e3f3eaf7467a"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Rb8a7b2842fcd45a1" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R505d839c3c0f4ced" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Ra366e3f3eaf7467a"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d7443d121774f17"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R505d839c3c0f4ced" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R2ad6fc4e0ffe41f7" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R5d7443d121774f17"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb7edcdaa994f4b5b"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R2ad6fc4e0ffe41f7" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R83a522dc40f34c2a" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rb7edcdaa994f4b5b"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7776594e56c4ddb"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R83a522dc40f34c2a" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Ra2bab34fe9704d83" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>
--- a/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
+++ b/tests/SafeOpenXml.Tests/Examples/Hyperlink_External/output.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rc7776594e56c4ddb"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="R088980a551d04892"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -53,7 +53,7 @@
     </x:row>
   </x:sheetData>
   <x:hyperlinks>
-    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="Ra2bab34fe9704d83" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
+    <x:hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="A1" r:id="R1add0aeb333f48c7" tooltip="Open in browser" display="dotnet/Open-XML-SDK"/>
   </x:hyperlinks>
 </x:worksheet>
 </file>